--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104465_W1.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104465_W1.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9548</v>
+        <v>7.1283</v>
       </c>
       <c r="E2" t="n">
-        <v>4.484</v>
+        <v>4.2141</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4709</v>
+        <v>2.9142</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3426</v>
+        <v>4.3352</v>
       </c>
       <c r="H2" t="n">
-        <v>3.0605</v>
+        <v>3.0589</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2821</v>
+        <v>1.2763</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9316</v>
+        <v>2.8975</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2036</v>
+        <v>3.1888</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.272</v>
+        <v>-0.2913</v>
       </c>
       <c r="M2" t="n">
-        <v>1.4111</v>
+        <v>1.4377</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O2" t="n">
-        <v>1.5541</v>
+        <v>1.5677</v>
       </c>
       <c r="P2" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1098</v>
+        <v>0.0615</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4597</v>
+        <v>0.2271</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5695</v>
+        <v>-0.1656</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ</t>
+          <t>T. BELL-HAYNES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9857</v>
+        <v>6.7414</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6001</v>
+        <v>2.8801</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3856</v>
+        <v>3.8613</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6019</v>
+        <v>6.9028</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.463</v>
+        <v>5.0616</v>
       </c>
       <c r="I3" t="n">
-        <v>4.0649</v>
+        <v>1.8413</v>
       </c>
       <c r="J3" t="n">
-        <v>2.814</v>
+        <v>5.6227</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5777</v>
+        <v>5.6085</v>
       </c>
       <c r="L3" t="n">
-        <v>2.2363</v>
+        <v>0.0142</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7879</v>
+        <v>1.2801</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0407</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>1.8286</v>
+        <v>1.827</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5878</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.361</v>
+        <v>-4.7803</v>
       </c>
       <c r="R3" t="n">
-        <v>2.9488</v>
+        <v>3.4145</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4745</v>
+        <v>-0.5876</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8257</v>
+        <v>0.2457</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3512</v>
+        <v>-0.8333</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3214</v>
+        <v>1.792</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3214</v>
+        <v>1.792</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. BELL-HAYNES</t>
+          <t>J. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.3758</v>
+        <v>5.653</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2481</v>
+        <v>2.1994</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1278</v>
+        <v>3.4536</v>
       </c>
       <c r="G4" t="n">
-        <v>6.9187</v>
+        <v>3.5918</v>
       </c>
       <c r="H4" t="n">
-        <v>5.0795</v>
+        <v>-0.4733</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8392</v>
+        <v>4.0652</v>
       </c>
       <c r="J4" t="n">
-        <v>5.6776</v>
+        <v>2.7739</v>
       </c>
       <c r="K4" t="n">
-        <v>5.6484</v>
+        <v>0.5474</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0292</v>
+        <v>2.2265</v>
       </c>
       <c r="M4" t="n">
-        <v>1.2412</v>
+        <v>0.8179</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5689</v>
+        <v>-1.0207</v>
       </c>
       <c r="O4" t="n">
-        <v>1.81</v>
+        <v>1.8386</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.7635</v>
+        <v>-1.3658</v>
       </c>
       <c r="R4" t="n">
-        <v>3.4025</v>
+        <v>2.9592</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.9816</v>
+        <v>0.1522</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4657</v>
+        <v>0.4757</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.5159</v>
+        <v>-0.3235</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7997</v>
+        <v>0.3155</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7997</v>
+        <v>0.3155</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0586</v>
+        <v>1.5379</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6081</v>
+        <v>4.0444</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.5495</v>
+        <v>-2.5065</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5135</v>
+        <v>0.5052</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3129</v>
+        <v>-0.3294</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8264</v>
+        <v>0.8345</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1033</v>
+        <v>2.0678</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3569</v>
+        <v>1.323</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7463</v>
+        <v>0.7447</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5897</v>
+        <v>-1.5626</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6698</v>
+        <v>-1.6524</v>
       </c>
       <c r="O5" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9799</v>
+        <v>0.4621</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5425</v>
+        <v>1.0285</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5626</v>
+        <v>-0.5664</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.7032</v>
+        <v>-1.7057</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1892</v>
+        <v>1.1758</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. GONZALEZ</t>
+          <t>B. DUBLJEVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.798</v>
+        <v>1.17</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7065</v>
+        <v>-1.1642</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9086</v>
+        <v>2.3341</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3279</v>
+        <v>0.7518</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.0391</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>2.367</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1126</v>
+        <v>-0.9989</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5266</v>
+        <v>0.4686</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6392</v>
+        <v>-1.4676</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7848000000000001</v>
+        <v>1.7507</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5125</v>
+        <v>-0.4603</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7277</v>
+        <v>2.211</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8162</v>
+        <v>0.1418</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8207</v>
+        <v>-0.1652</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0046</v>
+        <v>0.3071</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2534</v>
+        <v>-1.0895</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2534</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. DUBLJEVIC</t>
+          <t>M. GONZALEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3989</v>
+        <v>1.0271</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0314</v>
+        <v>2.0609</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4303</v>
+        <v>-1.0338</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7453</v>
+        <v>0.3383</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0043</v>
+        <v>-2.0256</v>
       </c>
       <c r="I7" t="n">
-        <v>0.741</v>
+        <v>2.3639</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.983</v>
+        <v>1.0997</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4778</v>
+        <v>-0.5311</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4608</v>
+        <v>1.6308</v>
       </c>
       <c r="M7" t="n">
-        <v>1.7283</v>
+        <v>-0.7613</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4735</v>
+        <v>-1.4945</v>
       </c>
       <c r="O7" t="n">
-        <v>2.2018</v>
+        <v>0.7331</v>
       </c>
       <c r="P7" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3853</v>
+        <v>1.0254</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0484</v>
+        <v>1.1888</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4337</v>
+        <v>-0.1634</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0927</v>
+        <v>-1.2472</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.262</v>
+        <v>-0.5601</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.3549</v>
+        <v>-3.5409</v>
       </c>
       <c r="F8" t="n">
-        <v>3.6169</v>
+        <v>2.9808</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0963</v>
+        <v>1.0737</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0659</v>
+        <v>-0.096</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1622</v>
+        <v>1.1697</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2034</v>
+        <v>-0.263</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6603</v>
+        <v>0.6088</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.8637</v>
+        <v>-0.8718</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2998</v>
+        <v>1.3366</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7261</v>
+        <v>-0.7048</v>
       </c>
       <c r="O8" t="n">
-        <v>2.0259</v>
+        <v>2.0415</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R8" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S8" t="n">
-        <v>1.419</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2511</v>
+        <v>0.1365</v>
       </c>
       <c r="U8" t="n">
-        <v>1.168</v>
+        <v>0.477</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7535</v>
+        <v>-1.1749</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9513</v>
+        <v>-0.3141</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8022</v>
+        <v>-0.8608</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5342</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6031</v>
+        <v>1.6054</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0689</v>
+        <v>-1.0696</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1567</v>
+        <v>1.138</v>
       </c>
       <c r="K9" t="n">
-        <v>2.5802</v>
+        <v>2.5683</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.4234</v>
+        <v>-1.4303</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6225000000000001</v>
+        <v>-0.6022</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9771</v>
+        <v>-0.9629</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3953</v>
+        <v>0.1707</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.747</v>
+        <v>-0.0863</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3517</v>
+        <v>0.257</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6545</v>
+        <v>-2.5643</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8436</v>
+        <v>-2.6667</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1891</v>
+        <v>0.1024</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7375</v>
+        <v>-1.7377</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8312</v>
+        <v>-0.8274</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9063</v>
+        <v>-0.9103</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5008</v>
+        <v>-1.5076</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2368</v>
+        <v>-0.2301</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8658</v>
+        <v>-0.8618</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6291</v>
+        <v>0.6317</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1685</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2087</v>
+        <v>-0.021</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0402</v>
+        <v>-0.0545</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2254</v>
+        <v>-3.4151</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6122</v>
+        <v>-0.8621</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6132</v>
+        <v>-2.553</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3802</v>
+        <v>-0.3756</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.254</v>
+        <v>-2.2464</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8738</v>
+        <v>1.8708</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3751</v>
+        <v>1.361</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3015</v>
+        <v>-0.307</v>
       </c>
       <c r="L11" t="n">
-        <v>1.6765</v>
+        <v>1.668</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7552</v>
+        <v>-1.7365</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9525</v>
+        <v>-1.9394</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9379</v>
+        <v>-0.129</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6775</v>
+        <v>0.1019</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2604</v>
+        <v>-0.2309</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>15.2004</v>
+        <v>15.5433</v>
       </c>
       <c r="E12" t="n">
-        <v>6.853400000000001</v>
+        <v>6.850900000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>8.347100000000001</v>
+        <v>8.692299999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>15.9627</v>
+        <v>15.9213</v>
       </c>
       <c r="H12" t="n">
-        <v>3.7813</v>
+        <v>3.736200000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>12.1814</v>
+        <v>12.1852</v>
       </c>
       <c r="J12" t="n">
-        <v>14.4837</v>
+        <v>14.1911</v>
       </c>
       <c r="K12" t="n">
-        <v>13.7114</v>
+        <v>13.5098</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7721999999999996</v>
+        <v>0.6812000000000005</v>
       </c>
       <c r="M12" t="n">
-        <v>1.4793</v>
+        <v>1.7303</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.93</v>
+        <v>-9.773699999999998</v>
       </c>
       <c r="O12" t="n">
-        <v>11.4091</v>
+        <v>11.504</v>
       </c>
       <c r="P12" t="n">
-        <v>4.5365</v>
+        <v>4.5525</v>
       </c>
       <c r="Q12" t="n">
-        <v>-15.8783</v>
+        <v>-15.9343</v>
       </c>
       <c r="R12" t="n">
-        <v>20.415</v>
+        <v>20.4869</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4818</v>
+        <v>1.8351</v>
       </c>
       <c r="T12" t="n">
-        <v>2.752400000000001</v>
+        <v>3.1317</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.2706</v>
+        <v>-1.2965</v>
       </c>
       <c r="V12" t="n">
-        <v>-6.781099999999999</v>
+        <v>-6.766100000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>5.4957</v>
+        <v>5.4623</v>
       </c>
       <c r="X12" t="n">
-        <v>-12.2767</v>
+        <v>-12.2282</v>
       </c>
     </row>
     <row r="13">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4322</v>
+        <v>3.4931</v>
       </c>
       <c r="E13" t="n">
-        <v>4.5949</v>
+        <v>4.3013</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1627</v>
+        <v>-0.8082</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.1753</v>
+        <v>-1.1736</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0216</v>
+        <v>0.0256</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.1968</v>
+        <v>-1.1992</v>
       </c>
       <c r="J13" t="n">
-        <v>1.2562</v>
+        <v>1.2203</v>
       </c>
       <c r="K13" t="n">
-        <v>1.7867</v>
+        <v>1.7647</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5306</v>
+        <v>-0.5443</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.4314</v>
+        <v>-2.394</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.7652</v>
+        <v>-1.739</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0166</v>
+        <v>0.0615</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5293</v>
+        <v>0.2968</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5459000000000001</v>
+        <v>-0.2353</v>
       </c>
       <c r="V13" t="n">
-        <v>5.0777</v>
+        <v>5.0604</v>
       </c>
       <c r="W13" t="n">
-        <v>5.0777</v>
+        <v>5.0604</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,58 +1501,58 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.099</v>
+        <v>2.7603</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4828</v>
+        <v>1.0623</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6162</v>
+        <v>1.698</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3204</v>
+        <v>2.3282</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5238</v>
+        <v>0.5255</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7966</v>
+        <v>1.8027</v>
       </c>
       <c r="J14" t="n">
-        <v>1.248</v>
+        <v>1.2368</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6509</v>
+        <v>0.641</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5971</v>
+        <v>0.5958</v>
       </c>
       <c r="M14" t="n">
-        <v>1.0724</v>
+        <v>1.0914</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O14" t="n">
-        <v>1.1995</v>
+        <v>1.2069</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1287</v>
+        <v>-0.4784</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7652</v>
+        <v>-0.1745</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3636</v>
+        <v>-0.3039</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7454</v>
+        <v>0.9147</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2955</v>
+        <v>0.1116</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4499</v>
+        <v>0.8031</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5254</v>
+        <v>0.5183</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8688</v>
+        <v>1.8588</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3434</v>
+        <v>-1.3405</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7069</v>
+        <v>1.6648</v>
       </c>
       <c r="K15" t="n">
-        <v>3.1303</v>
+        <v>3.0952</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.4234</v>
+        <v>-1.4303</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1815</v>
+        <v>-1.1466</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2615</v>
+        <v>-1.2364</v>
       </c>
       <c r="O15" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2104</v>
+        <v>0.4043</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4597</v>
+        <v>0.3456</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7506</v>
+        <v>0.0587</v>
       </c>
       <c r="V15" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="W15" t="n">
-        <v>2.8924</v>
+        <v>2.8814</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. DIOP</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.6083</v>
+        <v>-1.3375</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6304</v>
+        <v>-0.6698</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2387</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3554</v>
+        <v>-3.5187</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5527</v>
+        <v>-2.4388</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1973</v>
+        <v>-1.0799</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.111</v>
+        <v>-1.3664</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.111</v>
+        <v>-0.614</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0.7524</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2444</v>
+        <v>-2.1522</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4417</v>
+        <v>-1.8248</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1973</v>
+        <v>-0.3275</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4107</v>
+        <v>-0.2254</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8075</v>
+        <v>-0.1165</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3968</v>
+        <v>-0.1089</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.571</v>
+        <v>2.1789</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1607</v>
+        <v>2.1789</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.7317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.6205</v>
+        <v>-1.518</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2695</v>
+        <v>-0.8292</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.351</v>
+        <v>-0.6888</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.946</v>
+        <v>-1.7688</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7301</v>
+        <v>0.4076</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2159</v>
+        <v>-2.1764</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4298</v>
+        <v>0.5254</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3565</v>
+        <v>2.2613</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7864</v>
+        <v>-1.7359</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5162</v>
+        <v>-2.2941</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0867</v>
+        <v>-1.8536</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5705</v>
+        <v>-0.4405</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>0.284</v>
+        <v>-0.4321</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1603</v>
+        <v>-0.2164</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1237</v>
+        <v>-0.2157</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6543</v>
+        <v>-1.5389</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6456</v>
+        <v>-0.3978</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0087</v>
+        <v>-1.1411</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.5281</v>
+        <v>-0.944</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.4459</v>
+        <v>-0.7295</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0822</v>
+        <v>-0.2144</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.352</v>
+        <v>-0.4417</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.603</v>
+        <v>0.348</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.749</v>
+        <v>-0.7896</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1761</v>
+        <v>-0.5023</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.8429</v>
+        <v>-1.0775</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3331</v>
+        <v>0.5752</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5383</v>
+        <v>0.3564</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1179</v>
+        <v>0.0439</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4204</v>
+        <v>0.3126</v>
       </c>
       <c r="V18" t="n">
-        <v>2.1853</v>
+        <v>-1.6342</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>K. DIOP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0557</v>
+        <v>-1.9992</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.7882</v>
+        <v>0.1515</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7324</v>
+        <v>-2.1506</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.2977</v>
+        <v>-0.3459</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8024</v>
+        <v>-0.5488</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4954</v>
+        <v>0.2028</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.4616</v>
+        <v>-0.1174</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.1398</v>
+        <v>-0.1174</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.3218</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1638</v>
+        <v>-0.2285</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6626</v>
+        <v>-0.4314</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8264</v>
+        <v>0.2028</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0171</v>
+        <v>0.0022</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8075</v>
+        <v>0.3388</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2096</v>
+        <v>-0.3366</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2249</v>
+        <v>-2.5659</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
-        <v>0.2249</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4673</v>
+        <v>-2.6569</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1198</v>
+        <v>-1.3013</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3476</v>
+        <v>-1.3556</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.318</v>
+        <v>-0.3157</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1127</v>
+        <v>-0.1039</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2053</v>
+        <v>-0.2118</v>
       </c>
       <c r="J20" t="n">
-        <v>2.7552</v>
+        <v>2.7097</v>
       </c>
       <c r="K20" t="n">
-        <v>2.3928</v>
+        <v>2.368</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3623</v>
+        <v>0.3417</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.0732</v>
+        <v>-3.0253</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.5055</v>
+        <v>-2.4718</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5676</v>
+        <v>-0.5535</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2005</v>
+        <v>-0.382</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1815</v>
+        <v>0.0668</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.382</v>
+        <v>-0.4488</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>S. JOKSIMOVIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6924</v>
+        <v>-2.7509</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6236</v>
+        <v>-2.303</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0688</v>
+        <v>-0.4478</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7711</v>
+        <v>-2.4279</v>
       </c>
       <c r="H21" t="n">
-        <v>0.404</v>
+        <v>-1.4046</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.1751</v>
+        <v>-1.0234</v>
       </c>
       <c r="J21" t="n">
-        <v>0.554</v>
+        <v>-1.4386</v>
       </c>
       <c r="K21" t="n">
-        <v>2.2787</v>
+        <v>-0.6862</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.7247</v>
+        <v>-0.7524</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.3251</v>
+        <v>-0.9893</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.8747</v>
+        <v>-0.7184</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4504</v>
+        <v>-0.271</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6017</v>
+        <v>0.36</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0434</v>
+        <v>0.3436</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5583</v>
+        <v>0.0163</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. JOKSIMOVIC</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7365</v>
+        <v>-2.9251</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0541</v>
+        <v>-4.2794</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6824</v>
+        <v>1.3544</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4305</v>
+        <v>-3.2926</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4069</v>
+        <v>-1.7954</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0236</v>
+        <v>-1.4971</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.4315</v>
+        <v>-3.4801</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6825</v>
+        <v>-1.1484</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.749</v>
+        <v>-2.3317</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.999</v>
+        <v>0.1875</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7245</v>
+        <v>-0.6471</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2745</v>
+        <v>0.8345</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6805</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3744</v>
+        <v>0.1383</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5777</v>
+        <v>0.3388</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2032</v>
+        <v>-0.2005</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.2292</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.6419</v>
+        <v>-6.8467</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.9427</v>
+        <v>-5.628</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6993</v>
+        <v>-1.2187</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.9864</v>
+        <v>-4.9807</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4514</v>
+        <v>0.4673</v>
       </c>
       <c r="I23" t="n">
-        <v>-5.4378</v>
+        <v>-5.448</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.2136</v>
+        <v>-2.2432</v>
       </c>
       <c r="K23" t="n">
-        <v>1.8702</v>
+        <v>1.8616</v>
       </c>
       <c r="L23" t="n">
-        <v>-4.0838</v>
+        <v>-4.1048</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.7728</v>
+        <v>-2.7375</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4188</v>
+        <v>-1.3943</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2926</v>
+        <v>-0.5018</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3266</v>
+        <v>0.0297</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.966</v>
+        <v>-0.5315</v>
       </c>
       <c r="V23" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-15.2003</v>
+        <v>-14.4051</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.439899999999998</v>
+        <v>-9.7818</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.7607</v>
+        <v>-4.6231</v>
       </c>
       <c r="G24" t="n">
-        <v>-15.9627</v>
+        <v>-15.9214</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.7811</v>
+        <v>-3.7362</v>
       </c>
       <c r="I24" t="n">
-        <v>-12.1816</v>
+        <v>-12.1852</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.479199999999999</v>
+        <v>-1.7304</v>
       </c>
       <c r="K24" t="n">
-        <v>9.9298</v>
+        <v>9.7738</v>
       </c>
       <c r="L24" t="n">
-        <v>-11.4093</v>
+        <v>-11.5039</v>
       </c>
       <c r="M24" t="n">
-        <v>-14.4835</v>
+        <v>-14.1909</v>
       </c>
       <c r="N24" t="n">
-        <v>-13.7113</v>
+        <v>-13.5098</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7722000000000002</v>
+        <v>-0.6813999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>-4.536799999999999</v>
+        <v>-4.5527</v>
       </c>
       <c r="Q24" t="n">
-        <v>-20.415</v>
+        <v>-20.487</v>
       </c>
       <c r="R24" t="n">
-        <v>15.8784</v>
+        <v>15.9344</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4818</v>
+        <v>-0.6970000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>1.2704</v>
+        <v>1.2966</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.7523</v>
+        <v>-1.9936</v>
       </c>
       <c r="V24" t="n">
-        <v>6.7808</v>
+        <v>6.765999999999998</v>
       </c>
       <c r="W24" t="n">
-        <v>11.1839</v>
+        <v>11.1388</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.403</v>
+        <v>-4.3729</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104465_W1.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104465_W1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104465_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104465_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104465_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104465_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104465_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104465_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104465_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104465_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104465_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104465_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-12.2282</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104465_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104465_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104465_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104465_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104465_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104465_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104465_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104465_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104465_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104465_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104465_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-4.3729</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
